--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -63147,13 +63147,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O462" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="R462" t="n">
-        <v>0.8837142852491729</v>
+        <v>0.8817763153253809</v>
       </c>
       <c r="AA462" t="inlineStr">
         <is>
@@ -71000,13 +71000,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>5547</v>
+        <v>5544</v>
       </c>
       <c r="O520" t="n">
-        <v>5547</v>
+        <v>5544</v>
       </c>
       <c r="R520" t="n">
-        <v>10.74991916727448</v>
+        <v>10.7441052575031</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
@@ -73862,13 +73862,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O541" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R541" t="n">
-        <v>0.3217030073494796</v>
+        <v>0.3236409772732716</v>
       </c>
       <c r="U541" t="inlineStr">
         <is>
@@ -77107,13 +77107,13 @@
         </is>
       </c>
       <c r="N565" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O565" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R565" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="AA565" t="inlineStr">
         <is>
@@ -77242,13 +77242,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O566" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R566" t="n">
-        <v>0.1182161653513148</v>
+        <v>0.1201541352751068</v>
       </c>
       <c r="AA566" t="inlineStr">
         <is>
@@ -79816,13 +79816,13 @@
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5225</v>
+        <v>5222</v>
       </c>
       <c r="O585" t="n">
-        <v>5225</v>
+        <v>5222</v>
       </c>
       <c r="R585" t="n">
-        <v>10.12589285181344</v>
+        <v>10.12007894204206</v>
       </c>
       <c r="U585" t="inlineStr">
         <is>
@@ -80509,13 +80509,13 @@
         </is>
       </c>
       <c r="N590" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="O590" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="R590" t="n">
-        <v>0.1492236841319876</v>
+        <v>0.1821691728364523</v>
       </c>
       <c r="AA590" t="inlineStr">
         <is>
@@ -80644,13 +80644,13 @@
         </is>
       </c>
       <c r="N591" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O591" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R591" t="n">
-        <v>0.01550375939033637</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="AA591" t="inlineStr">
         <is>
@@ -80779,13 +80779,13 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="O592" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="R592" t="n">
-        <v>0.4127875937677058</v>
+        <v>0.4825545110242194</v>
       </c>
       <c r="AA592" t="inlineStr">
         <is>
@@ -80914,13 +80914,13 @@
         </is>
       </c>
       <c r="N593" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O593" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R593" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="AA593" t="inlineStr">
         <is>
@@ -81463,13 +81463,13 @@
         </is>
       </c>
       <c r="N597" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O597" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R597" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="AA597" t="inlineStr">
         <is>
@@ -81868,13 +81868,13 @@
         </is>
       </c>
       <c r="N600" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O600" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R600" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="AA600" t="inlineStr">
         <is>
@@ -82138,13 +82138,13 @@
         </is>
       </c>
       <c r="N602" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O602" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R602" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="AA602" t="inlineStr">
         <is>
@@ -82408,13 +82408,13 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="O604" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="R604" t="n">
-        <v>0.6976691725651365</v>
+        <v>0.8042575183736991</v>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
@@ -82678,13 +82678,13 @@
         </is>
       </c>
       <c r="N606" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O606" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="R606" t="n">
-        <v>0.1744172931412841</v>
+        <v>0.1860451126840364</v>
       </c>
       <c r="U606" t="inlineStr">
         <is>
@@ -82957,13 +82957,13 @@
         </is>
       </c>
       <c r="N608" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O608" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R608" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="AA608" t="inlineStr">
         <is>
@@ -83092,13 +83092,13 @@
         </is>
       </c>
       <c r="N609" t="n">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="O609" t="n">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="R609" t="n">
-        <v>0.4341052629294183</v>
+        <v>0.5019342102621399</v>
       </c>
       <c r="AA609" t="inlineStr">
         <is>
@@ -84172,13 +84172,13 @@
         </is>
       </c>
       <c r="N617" t="n">
-        <v>1040</v>
+        <v>1193</v>
       </c>
       <c r="O617" t="n">
-        <v>1040</v>
+        <v>1193</v>
       </c>
       <c r="R617" t="n">
-        <v>2.015488720743728</v>
+        <v>2.311998119083911</v>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
@@ -84307,13 +84307,13 @@
         </is>
       </c>
       <c r="N618" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="O618" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="R618" t="n">
-        <v>0.05813909771376138</v>
+        <v>0.07364285710409775</v>
       </c>
       <c r="AA618" t="inlineStr">
         <is>
@@ -84442,13 +84442,13 @@
         </is>
       </c>
       <c r="N619" t="n">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="O619" t="n">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="R619" t="n">
-        <v>0.296509398340183</v>
+        <v>0.4767406012528433</v>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
@@ -85383,13 +85383,13 @@
         </is>
       </c>
       <c r="N626" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O626" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R626" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
@@ -85518,13 +85518,13 @@
         </is>
       </c>
       <c r="N627" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O627" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R627" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.05813909771376138</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
@@ -85923,13 +85923,13 @@
         </is>
       </c>
       <c r="N630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R630" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA630" t="inlineStr">
         <is>
@@ -86058,13 +86058,13 @@
         </is>
       </c>
       <c r="N631" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O631" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R631" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
@@ -88632,13 +88632,13 @@
         </is>
       </c>
       <c r="N650" t="n">
-        <v>3005</v>
+        <v>3298</v>
       </c>
       <c r="O650" t="n">
-        <v>3005</v>
+        <v>3298</v>
       </c>
       <c r="R650" t="n">
-        <v>5.823599620995098</v>
+        <v>6.391424808666168</v>
       </c>
       <c r="U650" t="inlineStr">
         <is>
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95225</v>
+        <v>95938</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -67886,13 +67886,13 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O497" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R497" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1162781954275228</v>
       </c>
       <c r="AA497" t="inlineStr">
         <is>
@@ -71963,13 +71963,13 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="O527" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="R527" t="n">
-        <v>0.7829398492119866</v>
+        <v>0.7790639093644025</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
@@ -72917,13 +72917,13 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O534" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R534" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="AA534" t="inlineStr">
         <is>
@@ -75626,13 +75626,13 @@
         </is>
       </c>
       <c r="N554" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O554" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R554" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="AA554" t="inlineStr">
         <is>
@@ -79816,13 +79816,13 @@
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5222</v>
+        <v>5220</v>
       </c>
       <c r="O585" t="n">
-        <v>5222</v>
+        <v>5220</v>
       </c>
       <c r="R585" t="n">
-        <v>10.12007894204206</v>
+        <v>10.11620300219448</v>
       </c>
       <c r="U585" t="inlineStr">
         <is>
@@ -80644,13 +80644,13 @@
         </is>
       </c>
       <c r="N591" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O591" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R591" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="AA591" t="inlineStr">
         <is>
@@ -80779,13 +80779,13 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="O592" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="R592" t="n">
-        <v>0.4825545110242194</v>
+        <v>0.5135620298048922</v>
       </c>
       <c r="AA592" t="inlineStr">
         <is>
@@ -82408,13 +82408,13 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="O604" t="n">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="R604" t="n">
-        <v>0.8042575183736991</v>
+        <v>0.8372030070781639</v>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
@@ -82678,13 +82678,13 @@
         </is>
       </c>
       <c r="N606" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="O606" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="R606" t="n">
-        <v>0.1860451126840364</v>
+        <v>0.2015488720743728</v>
       </c>
       <c r="U606" t="inlineStr">
         <is>
@@ -82822,13 +82822,13 @@
         </is>
       </c>
       <c r="N607" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O607" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R607" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="AA607" t="inlineStr">
         <is>
@@ -82957,13 +82957,13 @@
         </is>
       </c>
       <c r="N608" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O608" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R608" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="AA608" t="inlineStr">
         <is>
@@ -83092,13 +83092,13 @@
         </is>
       </c>
       <c r="N609" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="O609" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="R609" t="n">
-        <v>0.5019342102621399</v>
+        <v>0.5154999997286842</v>
       </c>
       <c r="AA609" t="inlineStr">
         <is>
@@ -84172,13 +84172,13 @@
         </is>
       </c>
       <c r="N617" t="n">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="O617" t="n">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="R617" t="n">
-        <v>2.311998119083911</v>
+        <v>2.383703006264216</v>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
@@ -84307,13 +84307,13 @@
         </is>
       </c>
       <c r="N618" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O618" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R618" t="n">
-        <v>0.07364285710409775</v>
+        <v>0.07558082702788979</v>
       </c>
       <c r="AA618" t="inlineStr">
         <is>
@@ -84442,13 +84442,13 @@
         </is>
       </c>
       <c r="N619" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="O619" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="R619" t="n">
-        <v>0.4767406012528433</v>
+        <v>0.5193759395762684</v>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
@@ -84843,13 +84843,13 @@
         </is>
       </c>
       <c r="N622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R622" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
@@ -85518,13 +85518,13 @@
         </is>
       </c>
       <c r="N627" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O627" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R627" t="n">
-        <v>0.05813909771376138</v>
+        <v>0.06007706763755342</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
@@ -85923,13 +85923,13 @@
         </is>
       </c>
       <c r="N630" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O630" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R630" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="AA630" t="inlineStr">
         <is>
@@ -86058,13 +86058,13 @@
         </is>
       </c>
       <c r="N631" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O631" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R631" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
@@ -86328,13 +86328,13 @@
         </is>
       </c>
       <c r="N633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R633" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA633" t="inlineStr">
         <is>
@@ -86733,13 +86733,13 @@
         </is>
       </c>
       <c r="N636" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O636" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R636" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="AA636" t="inlineStr">
         <is>
@@ -88632,13 +88632,13 @@
         </is>
       </c>
       <c r="N650" t="n">
-        <v>3298</v>
+        <v>3349</v>
       </c>
       <c r="O650" t="n">
-        <v>3298</v>
+        <v>3349</v>
       </c>
       <c r="R650" t="n">
-        <v>6.391424808666168</v>
+        <v>6.490261274779561</v>
       </c>
       <c r="U650" t="inlineStr">
         <is>
@@ -88776,13 +88776,13 @@
         </is>
       </c>
       <c r="N651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R651" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="U651" t="inlineStr">
         <is>
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95938</v>
+        <v>96107</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -82408,13 +82408,13 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O604" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R604" t="n">
-        <v>0.8372030070781639</v>
+        <v>0.8430169168495401</v>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
@@ -85518,13 +85518,13 @@
         </is>
       </c>
       <c r="N627" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O627" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R627" t="n">
-        <v>0.06007706763755342</v>
+        <v>0.05813909771376138</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96107</v>
+        <v>96109</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -62877,13 +62877,13 @@
         </is>
       </c>
       <c r="N460" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O460" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R460" t="n">
-        <v>0.2558120299405501</v>
+        <v>0.2577499998643421</v>
       </c>
       <c r="AA460" t="inlineStr">
         <is>
@@ -63147,13 +63147,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O462" t="n">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="R462" t="n">
-        <v>0.8817763153253809</v>
+        <v>0.885652255172965</v>
       </c>
       <c r="AA462" t="inlineStr">
         <is>
@@ -71000,13 +71000,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>5544</v>
+        <v>5539</v>
       </c>
       <c r="O520" t="n">
-        <v>5544</v>
+        <v>5539</v>
       </c>
       <c r="R520" t="n">
-        <v>10.7441052575031</v>
+        <v>10.73441540788414</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
@@ -71693,13 +71693,13 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O525" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R525" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2441842103977978</v>
       </c>
       <c r="AA525" t="inlineStr">
         <is>
@@ -76702,13 +76702,13 @@
         </is>
       </c>
       <c r="N562" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O562" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R562" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="AA562" t="inlineStr">
         <is>
@@ -77107,13 +77107,13 @@
         </is>
       </c>
       <c r="N565" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O565" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R565" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="AA565" t="inlineStr">
         <is>
@@ -79816,13 +79816,13 @@
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5220</v>
+        <v>5219</v>
       </c>
       <c r="O585" t="n">
-        <v>5220</v>
+        <v>5219</v>
       </c>
       <c r="R585" t="n">
-        <v>10.11620300219448</v>
+        <v>10.11426503227069</v>
       </c>
       <c r="U585" t="inlineStr">
         <is>
@@ -80509,13 +80509,13 @@
         </is>
       </c>
       <c r="N590" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="O590" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="R590" t="n">
-        <v>0.1821691728364523</v>
+        <v>0.2189906013885012</v>
       </c>
       <c r="AA590" t="inlineStr">
         <is>
@@ -80644,13 +80644,13 @@
         </is>
       </c>
       <c r="N591" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O591" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R591" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="AA591" t="inlineStr">
         <is>
@@ -80779,13 +80779,13 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="O592" t="n">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="R592" t="n">
-        <v>0.5135620298048922</v>
+        <v>0.6220883455372467</v>
       </c>
       <c r="AA592" t="inlineStr">
         <is>
@@ -80914,13 +80914,13 @@
         </is>
       </c>
       <c r="N593" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O593" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R593" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="AA593" t="inlineStr">
         <is>
@@ -81463,13 +81463,13 @@
         </is>
       </c>
       <c r="N597" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O597" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R597" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="AA597" t="inlineStr">
         <is>
@@ -81733,13 +81733,13 @@
         </is>
       </c>
       <c r="N599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R599" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA599" t="inlineStr">
         <is>
@@ -81868,13 +81868,13 @@
         </is>
       </c>
       <c r="N600" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O600" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R600" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="AA600" t="inlineStr">
         <is>
@@ -82138,13 +82138,13 @@
         </is>
       </c>
       <c r="N602" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O602" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R602" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="AA602" t="inlineStr">
         <is>
@@ -82408,13 +82408,13 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>435</v>
+        <v>541</v>
       </c>
       <c r="O604" t="n">
-        <v>435</v>
+        <v>541</v>
       </c>
       <c r="R604" t="n">
-        <v>0.8430169168495401</v>
+        <v>1.048441728771497</v>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
@@ -82678,13 +82678,13 @@
         </is>
       </c>
       <c r="N606" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="O606" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="R606" t="n">
-        <v>0.2015488720743728</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="U606" t="inlineStr">
         <is>
@@ -82822,13 +82822,13 @@
         </is>
       </c>
       <c r="N607" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O607" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R607" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="AA607" t="inlineStr">
         <is>
@@ -83092,13 +83092,13 @@
         </is>
       </c>
       <c r="N609" t="n">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="O609" t="n">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="R609" t="n">
-        <v>0.5154999997286842</v>
+        <v>0.589142856832782</v>
       </c>
       <c r="AA609" t="inlineStr">
         <is>
@@ -83767,13 +83767,13 @@
         </is>
       </c>
       <c r="N614" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O614" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R614" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="AA614" t="inlineStr">
         <is>
@@ -84172,13 +84172,13 @@
         </is>
       </c>
       <c r="N617" t="n">
-        <v>1230</v>
+        <v>1467</v>
       </c>
       <c r="O617" t="n">
-        <v>1230</v>
+        <v>1467</v>
       </c>
       <c r="R617" t="n">
-        <v>2.383703006264216</v>
+        <v>2.843001878202931</v>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
@@ -84307,13 +84307,13 @@
         </is>
       </c>
       <c r="N618" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O618" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R618" t="n">
-        <v>0.07558082702788979</v>
+        <v>0.08720864657064206</v>
       </c>
       <c r="AA618" t="inlineStr">
         <is>
@@ -84442,13 +84442,13 @@
         </is>
       </c>
       <c r="N619" t="n">
-        <v>268</v>
+        <v>447</v>
       </c>
       <c r="O619" t="n">
-        <v>268</v>
+        <v>447</v>
       </c>
       <c r="R619" t="n">
-        <v>0.5193759395762684</v>
+        <v>0.8662725559350446</v>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
@@ -85248,13 +85248,13 @@
         </is>
       </c>
       <c r="N625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R625" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA625" t="inlineStr">
         <is>
@@ -85383,13 +85383,13 @@
         </is>
       </c>
       <c r="N626" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O626" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R626" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
@@ -85518,13 +85518,13 @@
         </is>
       </c>
       <c r="N627" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O627" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R627" t="n">
-        <v>0.05813909771376138</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
@@ -85923,13 +85923,13 @@
         </is>
       </c>
       <c r="N630" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O630" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R630" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="AA630" t="inlineStr">
         <is>
@@ -86058,13 +86058,13 @@
         </is>
       </c>
       <c r="N631" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="O631" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R631" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
@@ -86328,13 +86328,13 @@
         </is>
       </c>
       <c r="N633" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O633" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R633" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="AA633" t="inlineStr">
         <is>
@@ -86598,13 +86598,13 @@
         </is>
       </c>
       <c r="N635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R635" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="AA635" t="inlineStr">
         <is>
@@ -86733,13 +86733,13 @@
         </is>
       </c>
       <c r="N636" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O636" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R636" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="AA636" t="inlineStr">
         <is>
@@ -88632,13 +88632,13 @@
         </is>
       </c>
       <c r="N650" t="n">
-        <v>3349</v>
+        <v>4033</v>
       </c>
       <c r="O650" t="n">
-        <v>3349</v>
+        <v>4033</v>
       </c>
       <c r="R650" t="n">
-        <v>6.490261274779561</v>
+        <v>7.815832702653321</v>
       </c>
       <c r="U650" t="inlineStr">
         <is>
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96109</v>
+        <v>97502</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -71963,13 +71963,13 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O527" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="R527" t="n">
-        <v>0.7790639093644025</v>
+        <v>0.7810018792881945</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
@@ -77242,13 +77242,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O566" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R566" t="n">
-        <v>0.1201541352751068</v>
+        <v>0.1182161653513148</v>
       </c>
       <c r="AA566" t="inlineStr">
         <is>
@@ -79816,13 +79816,13 @@
         </is>
       </c>
       <c r="N585" t="n">
-        <v>5219</v>
+        <v>5217</v>
       </c>
       <c r="O585" t="n">
-        <v>5219</v>
+        <v>5217</v>
       </c>
       <c r="R585" t="n">
-        <v>10.11426503227069</v>
+        <v>10.1103890924231</v>
       </c>
       <c r="U585" t="inlineStr">
         <is>
@@ -80509,13 +80509,13 @@
         </is>
       </c>
       <c r="N590" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="O590" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="R590" t="n">
-        <v>0.2189906013885012</v>
+        <v>0.2325563908550455</v>
       </c>
       <c r="AA590" t="inlineStr">
         <is>
@@ -80779,13 +80779,13 @@
         </is>
       </c>
       <c r="N592" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="O592" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="R592" t="n">
-        <v>0.6220883455372467</v>
+        <v>0.631778195156207</v>
       </c>
       <c r="AA592" t="inlineStr">
         <is>
@@ -81463,13 +81463,13 @@
         </is>
       </c>
       <c r="N597" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O597" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R597" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="AA597" t="inlineStr">
         <is>
@@ -81868,13 +81868,13 @@
         </is>
       </c>
       <c r="N600" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O600" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R600" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="AA600" t="inlineStr">
         <is>
@@ -82138,13 +82138,13 @@
         </is>
       </c>
       <c r="N602" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O602" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R602" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="AA602" t="inlineStr">
         <is>
@@ -82408,13 +82408,13 @@
         </is>
       </c>
       <c r="N604" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="O604" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="R604" t="n">
-        <v>1.048441728771497</v>
+        <v>1.073635337780793</v>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
@@ -82678,13 +82678,13 @@
         </is>
       </c>
       <c r="N606" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="O606" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="R606" t="n">
-        <v>0.2403082705502137</v>
+        <v>0.2732537592546785</v>
       </c>
       <c r="U606" t="inlineStr">
         <is>
@@ -82822,13 +82822,13 @@
         </is>
       </c>
       <c r="N607" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O607" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R607" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="AA607" t="inlineStr">
         <is>
@@ -82957,13 +82957,13 @@
         </is>
       </c>
       <c r="N608" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O608" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R608" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="AA608" t="inlineStr">
         <is>
@@ -83092,13 +83092,13 @@
         </is>
       </c>
       <c r="N609" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="O609" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="R609" t="n">
-        <v>0.589142856832782</v>
+        <v>0.5968947365279502</v>
       </c>
       <c r="AA609" t="inlineStr">
         <is>
@@ -84172,13 +84172,13 @@
         </is>
       </c>
       <c r="N617" t="n">
-        <v>1467</v>
+        <v>1490</v>
       </c>
       <c r="O617" t="n">
-        <v>1467</v>
+        <v>1490</v>
       </c>
       <c r="R617" t="n">
-        <v>2.843001878202931</v>
+        <v>2.887575186450149</v>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
@@ -84442,13 +84442,13 @@
         </is>
       </c>
       <c r="N619" t="n">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="O619" t="n">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="R619" t="n">
-        <v>0.8662725559350446</v>
+        <v>0.9883646611339434</v>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
@@ -84843,13 +84843,13 @@
         </is>
       </c>
       <c r="N622" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O622" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R622" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
@@ -86058,13 +86058,13 @@
         </is>
       </c>
       <c r="N631" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O631" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R631" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
@@ -88632,13 +88632,13 @@
         </is>
       </c>
       <c r="N650" t="n">
-        <v>4033</v>
+        <v>4179</v>
       </c>
       <c r="O650" t="n">
-        <v>4033</v>
+        <v>4179</v>
       </c>
       <c r="R650" t="n">
-        <v>7.815832702653321</v>
+        <v>8.09877631152696</v>
       </c>
       <c r="U650" t="inlineStr">
         <is>
@@ -89031,7 +89031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>97502</v>
+        <v>97788</v>
       </c>
     </row>
     <row r="16">
